--- a/TestCase.xlsx
+++ b/TestCase.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\DataDrivenTesting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ADFD662-C13D-4BBD-90A9-DC658773FF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB993BC-932C-4062-B450-05CD2A2DDE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{61309A54-FECC-495E-80A6-D6F5A324B82F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="AllTestCase" sheetId="1" r:id="rId1"/>
+    <sheet name="AllError" sheetId="2" r:id="rId2"/>
+    <sheet name="ErrorStat" sheetId="3" r:id="rId3"/>
+    <sheet name="TestReport" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="369">
   <si>
     <t>TC ID</t>
   </si>
@@ -1442,12 +1448,445 @@
       <t>(Xóa mất ResponseCode)</t>
     </r>
   </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Tiêu đề</t>
+  </si>
+  <si>
+    <t>Mức độ</t>
+  </si>
+  <si>
+    <t>Ưu tiên</t>
+  </si>
+  <si>
+    <t>Bước tái hiện</t>
+  </si>
+  <si>
+    <t>Ảnh/Video</t>
+  </si>
+  <si>
+    <t>BUG001</t>
+  </si>
+  <si>
+    <t>Sai thông báo lỗi khi giỏ hàng có giá trị âm</t>
+  </si>
+  <si>
+    <t>Mã giảm giá</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>1. Nhập giỏ hàng có tổng tiền: -1đ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Áp dụng mã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>NEWBIE10</t>
+    </r>
+  </si>
+  <si>
+    <t>Báo lỗi: "Đơn hàng tối thiểu phải từ 0đ!"</t>
+  </si>
+  <si>
+    <t>Báo lỗi: "không hợp lệ" (từ chối giỏ hàng âm ngay lập tức)</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>(N/A)</t>
+  </si>
+  <si>
+    <t>BUG002</t>
+  </si>
+  <si>
+    <t>Lỗi sai số thập phân khi tính toán chiết khấu</t>
+  </si>
+  <si>
+    <t>Trivial</t>
+  </si>
+  <si>
+    <t>1. Tạo giỏ hàng cực lớn: 9,999,999,999đ</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Áp dụng mã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>NEWBIE10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (giảm 10%)</t>
+    </r>
+  </si>
+  <si>
+    <t>Kết quả tính ra: 999999999.9000001</t>
+  </si>
+  <si>
+    <t>Kết quả phải làm tròn: 999999999</t>
+  </si>
+  <si>
+    <t>BUG003</t>
+  </si>
+  <si>
+    <t>Không áp dụng được mã giảm giá khi dư khoảng trắng</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Nhập mã giảm giá: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>" FREES2 "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (dư khoảng trắng)</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Gửi API áp dụng mã</t>
+  </si>
+  <si>
+    <t>Trả về lỗi 400 (Mã không tồn tại)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trả về 200, API phải tự động cắt khoảng trắng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>.strip()</t>
+    </r>
+  </si>
+  <si>
+    <t>BUG004</t>
+  </si>
+  <si>
+    <t>Sập Server (Lỗi 500) khi gửi số lượng kiểu chuỗi (String)</t>
+  </si>
+  <si>
+    <t>Đặt hàng</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>1. Chọn mua sản phẩm.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Gửi số lượng dạng chuỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"1"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì số </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> qua API</t>
+    </r>
+  </si>
+  <si>
+    <t>API bị Crash, quăng lỗi 500 Internal Server Error</t>
+  </si>
+  <si>
+    <t>Trả về 201 (API tự ép kiểu) hoặc 400 (Báo lỗi sai định dạng)</t>
+  </si>
+  <si>
+    <t>BUG005</t>
+  </si>
+  <si>
+    <t>Hệ thống cho phép mua hàng với số lượng thập phân (Float)</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>1. Chọn mua đĩa than.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Nhập số lượng mua là: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>1.5</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Gửi API tạo đơn</t>
+  </si>
+  <si>
+    <t>Tạo đơn hàng thành công (HTTP 201) với số lượng 1.5</t>
+  </si>
+  <si>
+    <t>Báo lỗi 400: Không cho phép mua lẻ sản phẩm vật lý</t>
+  </si>
+  <si>
+    <t>BUG006</t>
+  </si>
+  <si>
+    <r>
+      <t>Chấp nhận số lượng kiểu Boolean (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Nhập số lượng là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>True</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo đơn hàng thành công (HTTP 201), ép </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>True = 1</t>
+    </r>
+  </si>
+  <si>
+    <t>Báo lỗi 400 do sai kiểu dữ liệu số lượng</t>
+  </si>
+  <si>
+    <t>BUG007</t>
+  </si>
+  <si>
+    <t>Tìm kiếm không ra kết quả khi gõ tiếng Việt không dấu</t>
+  </si>
+  <si>
+    <t>Tìm kiếm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Nhập từ khóa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>"thang"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> vào ô tìm kiếm</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Gửi API Search</t>
+  </si>
+  <si>
+    <t>Trả về mảng rỗng (0 sản phẩm)</t>
+  </si>
+  <si>
+    <t>Trả về 2 sản phẩm có chứa từ "Thắng"</t>
+  </si>
+  <si>
+    <t>BUG008</t>
+  </si>
+  <si>
+    <t>Tìm kiếm không ra kết quả khi từ khóa dư khoảng trắng</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Nhập từ khóa </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>" Thắng "</t>
+    </r>
+  </si>
+  <si>
+    <t>Trả về 2 sản phẩm (API phải tự xử lý khoảng trắng)</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION REPORT</t>
+  </si>
+  <si>
+    <t>Project Name:</t>
+  </si>
+  <si>
+    <t>ArchClub E-Commerce</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>Module/Feature:</t>
+  </si>
+  <si>
+    <t>Backend API</t>
+  </si>
+  <si>
+    <t>Tested By:</t>
+  </si>
+  <si>
+    <t>Function Name</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Quản lý Mã giảm giá</t>
+  </si>
+  <si>
+    <t>Tìm kiếm &amp; Lọc</t>
+  </si>
+  <si>
+    <t>Tồn kho &amp; Đặt hàng</t>
+  </si>
+  <si>
+    <t>Xác thực Form Checkout</t>
+  </si>
+  <si>
+    <t>Cổng thanh toán VNPay</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thái</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1493,16 +1932,48 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E2E2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1525,11 +1996,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -1553,6 +2076,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1568,6 +2128,338 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="110"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="10"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Test Status (Pass/Fail)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Test Status (Pass/Fail)</c:v>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1D70B8"/>
+              </a:solidFill>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F46C-41DD-99A6-94C738A0DD0D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="D4351C"/>
+              </a:solidFill>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F46C-41DD-99A6-94C738A0DD0D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Dashboard!$B$6:$C$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Dashboard!$B$12:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-F46C-41DD-99A6-94C738A0DD0D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>153017</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>119496</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>34527</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37B851AB-3625-8178-5265-28424B761D52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="590550" y="343517"/>
+          <a:ext cx="5624946" cy="4453510"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>342901</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>400051</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>162881</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5251D2E-7C65-E200-BF0E-D5A6FAC8EDA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6438901" y="352425"/>
+          <a:ext cx="6153150" cy="4382456"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C222CCC1-C9BB-4369-9711-733E8AD7FAE5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dashboard"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>Passed</v>
+          </cell>
+          <cell r="C6" t="str">
+            <v>Failed</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>49</v>
+          </cell>
+          <cell r="C12">
+            <v>8</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3819,4 +4711,788 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C91A1C11-FCE2-4E2F-AC89-6CCE0A8A85CA}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="53.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="17"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="72">
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="E25:E27"/>
+    <mergeCell ref="G25:G27"/>
+    <mergeCell ref="H25:H27"/>
+    <mergeCell ref="I25:I27"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="H14:H18"/>
+    <mergeCell ref="I14:I18"/>
+    <mergeCell ref="J14:J18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="C14:C18"/>
+    <mergeCell ref="D14:D18"/>
+    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="G14:G18"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="G2:G4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7580C4E1-FE14-4C5E-8B13-67B2D1526D07}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FCAE8C8-C623-4562-BAB6-2C57E9B3C386}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" style="20" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="20" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75">
+      <c r="A1" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="B7" s="22">
+        <v>12</v>
+      </c>
+      <c r="C7" s="22">
+        <v>3</v>
+      </c>
+      <c r="D7" s="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="22">
+        <v>14</v>
+      </c>
+      <c r="C8" s="22">
+        <v>2</v>
+      </c>
+      <c r="D8" s="22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="B9" s="22">
+        <v>9</v>
+      </c>
+      <c r="C9" s="22">
+        <v>3</v>
+      </c>
+      <c r="D9" s="22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="B10" s="22">
+        <v>10</v>
+      </c>
+      <c r="C10" s="22">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="B11" s="22">
+        <v>4</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="21">
+        <v>49</v>
+      </c>
+      <c r="C12" s="21">
+        <v>8</v>
+      </c>
+      <c r="D12" s="21">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>